--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:18</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>128.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>91.27</v>
+        <v>91.26</v>
       </c>
     </row>
     <row r="3">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:45</t>
+    <t xml:space="preserve">2026-10-05 04:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,10 +493,10 @@
         <v>37.36</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>128.62</v>
+        <v>128.63</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>91.26</v>
+        <v>91.27</v>
       </c>
     </row>
     <row r="3">
